--- a/utils/monday_sprint_sprint_2024-28.xlsx
+++ b/utils/monday_sprint_sprint_2024-28.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="173">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>23920</t>
+    <t>5813640104</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>08/01/2024</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>04/02/2024</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,12 +102,15 @@
     <t>Janeiro</t>
   </si>
   <si>
-    <t>23861</t>
+    <t>5813955306</t>
   </si>
   <si>
     <t>REORGANIZAR DADOS</t>
   </si>
   <si>
+    <t>23/01/2024</t>
+  </si>
+  <si>
     <t>5905967091</t>
   </si>
   <si>
@@ -132,7 +135,7 @@
     <t>5905967357</t>
   </si>
   <si>
-    <t>6090</t>
+    <t>5539974009</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -144,13 +147,16 @@
     <t>20/11/2023</t>
   </si>
   <si>
+    <t>31/01/2024</t>
+  </si>
+  <si>
     <t>Semana 3</t>
   </si>
   <si>
     <t>Novembro</t>
   </si>
   <si>
-    <t>22994</t>
+    <t>5820026513</t>
   </si>
   <si>
     <t>Realizar integração via API de software Efact - CRP</t>
@@ -159,43 +165,64 @@
     <t>09/01/2024</t>
   </si>
   <si>
+    <t>01/02/2024</t>
+  </si>
+  <si>
+    <t>5894599483</t>
+  </si>
+  <si>
     <t>Realizar integração via API de software Efact - Dados Mestres</t>
   </si>
   <si>
     <t>19/01/2024</t>
   </si>
   <si>
-    <t>23628</t>
+    <t>5894635340</t>
   </si>
   <si>
     <t>Automação de planilha controle Ronda</t>
   </si>
   <si>
+    <t>5920951865</t>
+  </si>
+  <si>
     <t>Automação de planilha controle Ronda - Criação de Modelo</t>
   </si>
   <si>
     <t>24/01/2024</t>
   </si>
   <si>
+    <t>5920951516</t>
+  </si>
+  <si>
     <t>Automação de planilha controle Ronda - Incorporar tabela Base</t>
   </si>
   <si>
+    <t>5920951265</t>
+  </si>
+  <si>
     <t>Automação de planilha controle Ronda - Upload de Fotos</t>
   </si>
   <si>
+    <t>5920950581</t>
+  </si>
+  <si>
     <t>Automação de planilha controle Ronda - Criação da Tabela de dados</t>
   </si>
   <si>
+    <t>5920950167</t>
+  </si>
+  <si>
     <t>Automação de planilha controle Ronda - Desenvolver tela de entrada de dados</t>
   </si>
   <si>
-    <t>23838</t>
+    <t>5920885791</t>
   </si>
   <si>
     <t>Ordem de Coleta e Entrega - Coleta</t>
   </si>
   <si>
-    <t>22972</t>
+    <t>5539917524</t>
   </si>
   <si>
     <t>Integração das informações de proforma/invoices - Benner - Contabilização</t>
@@ -204,7 +231,7 @@
     <t>Alta</t>
   </si>
   <si>
-    <t>22695</t>
+    <t>5703642058</t>
   </si>
   <si>
     <t>Dasboard desmoldagem</t>
@@ -216,13 +243,13 @@
     <t>Dezembro</t>
   </si>
   <si>
-    <t>24040</t>
+    <t>5893496880</t>
   </si>
   <si>
     <t>Data de entrada no lançamento de notas do ERP</t>
   </si>
   <si>
-    <t>23339</t>
+    <t>5610807535</t>
   </si>
   <si>
     <t>ANDAMENTO AÇÕES - PROJETO POSTO DE CÓPIAS ELETRÔNICO</t>
@@ -231,88 +258,91 @@
     <t>01/12/2023</t>
   </si>
   <si>
+    <t>28/01/2024</t>
+  </si>
+  <si>
     <t>Semana 1</t>
   </si>
   <si>
-    <t>23313</t>
+    <t>5610991408</t>
   </si>
   <si>
     <t>Desenvolver Consistência Apontamento de Horas - PINTURA</t>
   </si>
   <si>
-    <t>24024</t>
+    <t>5893528272</t>
   </si>
   <si>
     <t>Reativar a coluna</t>
   </si>
   <si>
-    <t>23310</t>
+    <t>5611006782</t>
   </si>
   <si>
     <t>Desenvolver Consistência Apontamento de Horas - ACABAMENTO</t>
   </si>
   <si>
-    <t>24023</t>
+    <t>5893540517</t>
   </si>
   <si>
     <t>Remover Botão</t>
   </si>
   <si>
-    <t>24044</t>
+    <t>5893484605</t>
   </si>
   <si>
     <t>Sistema de Embarque</t>
   </si>
   <si>
-    <t>24018</t>
+    <t>5893553490</t>
   </si>
   <si>
     <t>Sistemas invoice - Exportação Invoice FN Documentos Benner</t>
   </si>
   <si>
-    <t>23306</t>
+    <t>5611015973</t>
   </si>
   <si>
     <t>Desenvolver Consistência Apontamento de Horas - MOLDAGEM UPR</t>
   </si>
   <si>
-    <t>23304</t>
+    <t>5611021166</t>
   </si>
   <si>
     <t>Desenvolver Consistência Apontamento de Horas - MOLDAGEM USE/ULE</t>
   </si>
   <si>
-    <t>24181</t>
+    <t>5893115838</t>
   </si>
   <si>
     <t>Inclusão de coluna na Planilha</t>
   </si>
   <si>
-    <t>24173</t>
+    <t>5893138329</t>
   </si>
   <si>
     <t>Relatório ERP</t>
   </si>
   <si>
-    <t>24146</t>
+    <t>5893292741</t>
   </si>
   <si>
     <t>Atualização Fluxos de Pré-Produtivo</t>
   </si>
   <si>
-    <t>23309</t>
+    <t>5611012180</t>
   </si>
   <si>
     <t>Desenvolver Consistência Apontamento de Horas - Apontamento Solda - Revisar</t>
   </si>
   <si>
-    <t>24161</t>
+    <t>5894888287</t>
   </si>
   <si>
     <t>Lcto de Venda para entrega futura</t>
   </si>
   <si>
-    <t>24086</t>
+    <t>5903645717</t>
   </si>
   <si>
     <t>Correção</t>
@@ -321,73 +351,88 @@
     <t>Bug Sistema de Inventário da Expedição</t>
   </si>
   <si>
-    <t>24140</t>
+    <t>5893330863</t>
   </si>
   <si>
     <t>Erro no sistema de desmoldagem</t>
   </si>
   <si>
-    <t>24111</t>
+    <t>5893364460</t>
   </si>
   <si>
     <t>TV de OS Pendentes Manutenção</t>
   </si>
   <si>
-    <t>24144</t>
+    <t>21/01/2024</t>
+  </si>
+  <si>
+    <t>5893315141</t>
   </si>
   <si>
     <t>SETOR 579 virar pendência</t>
   </si>
   <si>
-    <t>24090</t>
+    <t>5893390386</t>
   </si>
   <si>
     <t>Altona || Sistema ERP || Integrator - Alteração e Exportação Notas</t>
   </si>
   <si>
-    <t>24072</t>
+    <t>5893421271</t>
   </si>
   <si>
     <t>Aviso de alteração de saldo depósito</t>
   </si>
   <si>
-    <t>24060</t>
+    <t>5893461858</t>
   </si>
   <si>
     <t>Desenvolver Consistência Apontamento de Horas - ACABAMENTO Deltractor</t>
   </si>
   <si>
-    <t>24231</t>
+    <t>5912538085</t>
   </si>
   <si>
     <t>Altona || Sistema ERP || Cadastro de Materiais</t>
   </si>
   <si>
-    <t>23/01/2024</t>
-  </si>
-  <si>
-    <t>23870</t>
+    <t>5914885484</t>
   </si>
   <si>
     <t>Inserir nova coluna na máscara MPS</t>
   </si>
   <si>
-    <t>24245</t>
+    <t>5916648491</t>
   </si>
   <si>
     <t>Portal de pendências - compras x fiscal</t>
   </si>
   <si>
+    <t>30/01/2024</t>
+  </si>
+  <si>
+    <t>5920982469</t>
+  </si>
+  <si>
     <t>Portal de pendências - compras x fiscal  -Envio de pendência ao compras</t>
   </si>
   <si>
+    <t>5920982194</t>
+  </si>
+  <si>
     <t>Portal de pendências - compras x fiscal - Relatório / consulta no fiscal</t>
   </si>
   <si>
+    <t>5920981884</t>
+  </si>
+  <si>
     <t>Portal de pendências - compras x fiscal Comunicação das pendências</t>
   </si>
   <si>
-    <t>24205</t>
+    <t>29/01/2024</t>
+  </si>
+  <si>
+    <t>5894871552</t>
   </si>
   <si>
     <t>Criar rotina para importar automaticamente frete sobre entradas</t>
@@ -399,7 +444,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2024-28</t>
+    <t>Nov/2023</t>
   </si>
   <si>
     <t>Base</t>
@@ -469,6 +514,9 @@
   </si>
   <si>
     <t>Fazendo</t>
+  </si>
+  <si>
+    <t>Semana 5</t>
   </si>
   <si>
     <t>Homologação</t>
@@ -1044,7 +1092,7 @@
         <v>23</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>25</v>
@@ -1061,25 +1109,25 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>21</v>
@@ -1088,7 +1136,7 @@
         <v>22</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>24</v>
@@ -1100,7 +1148,7 @@
         <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>28</v>
@@ -1108,25 +1156,25 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>21</v>
@@ -1135,7 +1183,7 @@
         <v>22</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>24</v>
@@ -1147,7 +1195,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>28</v>
@@ -1155,25 +1203,25 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>21</v>
@@ -1182,7 +1230,7 @@
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>24</v>
@@ -1194,7 +1242,7 @@
         <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>28</v>
@@ -1202,22 +1250,22 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
@@ -1229,10 +1277,10 @@
         <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1241,30 +1289,30 @@
         <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>20</v>
@@ -1276,10 +1324,10 @@
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1296,46 +1344,46 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N9" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>28</v>
@@ -1343,7 +1391,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1355,10 +1403,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
@@ -1370,7 +1418,7 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>24</v>
@@ -1382,7 +1430,7 @@
         <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>28</v>
@@ -1390,7 +1438,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1402,10 +1450,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
@@ -1417,10 +1465,10 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1429,7 +1477,7 @@
         <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>28</v>
@@ -1437,38 +1485,38 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
       </c>
@@ -1476,7 +1524,7 @@
         <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>28</v>
@@ -1484,7 +1532,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1496,10 +1544,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1511,7 +1559,7 @@
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>24</v>
@@ -1523,7 +1571,7 @@
         <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>28</v>
@@ -1531,7 +1579,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1543,10 +1591,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1558,10 +1606,10 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1570,7 +1618,7 @@
         <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>28</v>
@@ -1578,7 +1626,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1590,10 +1638,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1605,7 +1653,7 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>24</v>
@@ -1617,7 +1665,7 @@
         <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>28</v>
@@ -1625,34 +1673,34 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>24</v>
@@ -1664,7 +1712,7 @@
         <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>28</v>
@@ -1672,7 +1720,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1684,13 +1732,13 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>21</v>
@@ -1699,10 +1747,10 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1711,15 +1759,15 @@
         <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1731,10 +1779,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -1746,7 +1794,7 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>24</v>
@@ -1758,15 +1806,15 @@
         <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1778,10 +1826,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -1793,10 +1841,10 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -1805,7 +1853,7 @@
         <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>28</v>
@@ -1813,7 +1861,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1825,10 +1873,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -1840,10 +1888,10 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1852,15 +1900,15 @@
         <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -1872,10 +1920,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -1887,10 +1935,10 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -1899,15 +1947,15 @@
         <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1919,10 +1967,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -1934,10 +1982,10 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -1946,7 +1994,7 @@
         <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>28</v>
@@ -1954,7 +2002,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -1966,10 +2014,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -1981,10 +2029,10 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -1993,15 +2041,15 @@
         <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2013,10 +2061,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -2028,10 +2076,10 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -2040,7 +2088,7 @@
         <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>28</v>
@@ -2048,38 +2096,38 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="K25" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
       </c>
@@ -2087,7 +2135,7 @@
         <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>28</v>
@@ -2095,7 +2143,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2107,10 +2155,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2122,7 +2170,7 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>24</v>
@@ -2134,7 +2182,7 @@
         <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>28</v>
@@ -2142,7 +2190,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2154,10 +2202,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2169,10 +2217,10 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2181,15 +2229,15 @@
         <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2201,10 +2249,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -2216,10 +2264,10 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2228,15 +2276,15 @@
         <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2248,10 +2296,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2263,10 +2311,10 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2275,7 +2323,7 @@
         <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>28</v>
@@ -2283,7 +2331,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2295,10 +2343,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -2310,10 +2358,10 @@
         <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2322,7 +2370,7 @@
         <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>28</v>
@@ -2330,7 +2378,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2342,10 +2390,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2357,10 +2405,10 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2369,7 +2417,7 @@
         <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>28</v>
@@ -2377,7 +2425,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2389,10 +2437,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
@@ -2404,7 +2452,7 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>24</v>
@@ -2416,15 +2464,15 @@
         <v>26</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2436,10 +2484,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -2451,10 +2499,10 @@
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -2463,7 +2511,7 @@
         <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O33" s="2" t="s">
         <v>28</v>
@@ -2471,22 +2519,22 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
@@ -2498,10 +2546,10 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -2510,7 +2558,7 @@
         <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O34" s="2" t="s">
         <v>28</v>
@@ -2518,7 +2566,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2530,10 +2578,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2545,10 +2593,10 @@
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
@@ -2557,7 +2605,7 @@
         <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O35" s="2" t="s">
         <v>28</v>
@@ -2565,7 +2613,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2577,10 +2625,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -2592,10 +2640,10 @@
         <v>22</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
@@ -2604,7 +2652,7 @@
         <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>28</v>
@@ -2612,7 +2660,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2624,10 +2672,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
@@ -2639,10 +2687,10 @@
         <v>22</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>25</v>
@@ -2651,7 +2699,7 @@
         <v>26</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>28</v>
@@ -2659,7 +2707,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -2671,10 +2719,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
@@ -2686,10 +2734,10 @@
         <v>22</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>25</v>
@@ -2698,7 +2746,7 @@
         <v>26</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>28</v>
@@ -2706,7 +2754,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
@@ -2718,10 +2766,10 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>20</v>
@@ -2733,10 +2781,10 @@
         <v>22</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>25</v>
@@ -2745,7 +2793,7 @@
         <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O39" s="2" t="s">
         <v>28</v>
@@ -2753,7 +2801,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
@@ -2765,10 +2813,10 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>20</v>
@@ -2780,7 +2828,7 @@
         <v>22</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>24</v>
@@ -2792,7 +2840,7 @@
         <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>28</v>
@@ -2800,7 +2848,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
@@ -2812,13 +2860,13 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>21</v>
@@ -2827,10 +2875,10 @@
         <v>22</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>116</v>
+        <v>31</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>25</v>
@@ -2839,7 +2887,7 @@
         <v>26</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O41" s="2" t="s">
         <v>28</v>
@@ -2847,7 +2895,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
@@ -2859,10 +2907,10 @@
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>20</v>
@@ -2874,10 +2922,10 @@
         <v>22</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>116</v>
+        <v>31</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>25</v>
@@ -2886,7 +2934,7 @@
         <v>26</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O42" s="2" t="s">
         <v>28</v>
@@ -2894,7 +2942,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
@@ -2906,10 +2954,10 @@
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>20</v>
@@ -2921,10 +2969,10 @@
         <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>116</v>
+        <v>31</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>131</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>25</v>
@@ -2933,7 +2981,7 @@
         <v>26</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O43" s="2" t="s">
         <v>28</v>
@@ -2941,7 +2989,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
@@ -2953,10 +3001,10 @@
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>20</v>
@@ -2968,10 +3016,10 @@
         <v>22</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>25</v>
@@ -2980,7 +3028,7 @@
         <v>26</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O44" s="2" t="s">
         <v>28</v>
@@ -2988,7 +3036,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
@@ -3000,10 +3048,10 @@
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>20</v>
@@ -3015,10 +3063,10 @@
         <v>22</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>131</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>25</v>
@@ -3027,7 +3075,7 @@
         <v>26</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O45" s="2" t="s">
         <v>28</v>
@@ -3035,7 +3083,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
@@ -3047,10 +3095,10 @@
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>20</v>
@@ -3062,10 +3110,10 @@
         <v>22</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>138</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>25</v>
@@ -3074,7 +3122,7 @@
         <v>26</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O46" s="2" t="s">
         <v>28</v>
@@ -3082,7 +3130,7 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
@@ -3094,10 +3142,10 @@
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>20</v>
@@ -3109,10 +3157,10 @@
         <v>22</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>25</v>
@@ -3121,7 +3169,7 @@
         <v>26</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O47" s="2" t="s">
         <v>28</v>
@@ -3140,23 +3188,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="B2" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="D2" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="E2" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -3164,16 +3212,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3184,7 +3232,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>20.46</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -3192,7 +3240,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -3205,7 +3253,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -3213,7 +3261,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -3244,12 +3292,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="B2">
         <v>46</v>
@@ -3263,7 +3311,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>20.46</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -3273,25 +3321,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -3308,13 +3356,13 @@
         <v>39</v>
       </c>
       <c r="G10" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -3326,21 +3374,21 @@
         <v>46</v>
       </c>
       <c r="P10" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="Q10">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="G11" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -3352,21 +3400,21 @@
         <v>46</v>
       </c>
       <c r="M11" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="Q11">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -3378,59 +3426,59 @@
         <v>41</v>
       </c>
       <c r="J12" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="Q12">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>36</v>
+        <v>167</v>
       </c>
       <c r="Q13">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H14">
         <v>4</v>
       </c>
       <c r="M14" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -3438,7 +3486,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -3446,7 +3494,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -3454,7 +3502,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -3462,10 +3510,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -3473,7 +3521,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -3487,7 +3535,7 @@
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>19</v>
@@ -3495,128 +3543,128 @@
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>52</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
